--- a/SCH-STH/Impact assessments/STP/st_sch_sth_impact_2502_1_school.xlsx
+++ b/SCH-STH/Impact assessments/STP/st_sch_sth_impact_2502_1_school.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\SCH-STH\Impact assessments\STP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D349F34-F370-46E2-99FF-DA58022A6300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA4F938-01D0-48E8-8F59-51ED2135374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -1481,9 +1481,6 @@
     <t>Si oui, quelle est le type détablissement?</t>
   </si>
   <si>
-    <t>A quelle distance se situe l'établissement de soin</t>
-  </si>
-  <si>
     <t>w_ets_soin_proche</t>
   </si>
   <si>
@@ -1496,10 +1493,13 @@
     <t>${w_ets_soin_proche} = 'Oui'</t>
   </si>
   <si>
-    <t>st_sch_sth_impact_2502_1_school</t>
-  </si>
-  <si>
-    <t>(2025 Fev) - 1. SCH/STH – Ecole/Localité</t>
+    <t>st_sch_sth_impact_2502_1_school_v2</t>
+  </si>
+  <si>
+    <t>(2025 Fev) - 1. SCH/STH – Ecole/Localité V2</t>
+  </si>
+  <si>
+    <t>A quelle distance en KM se situe l'établissement de soin</t>
   </si>
 </sst>
 </file>
@@ -2258,14 +2258,13 @@
       <c r="L4" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="M4" s="29"/>
+      <c r="M4" s="29" t="s">
+        <v>158</v>
+      </c>
       <c r="N4" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="O4" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="P4" s="29"/>
+      <c r="O4" s="29"/>
     </row>
     <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
@@ -2291,11 +2290,10 @@
         <v>356</v>
       </c>
       <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
+      <c r="N5" s="29" t="s">
+        <v>159</v>
+      </c>
       <c r="O5" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="P5" s="29" t="s">
         <v>157</v>
       </c>
     </row>
@@ -2688,7 +2686,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>463</v>
@@ -2714,7 +2712,7 @@
         <v>45</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>464</v>
@@ -2724,7 +2722,7 @@
       <c r="F21" s="20"/>
       <c r="G21" s="19"/>
       <c r="H21" s="33" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I21" s="20"/>
       <c r="J21" s="9" t="s">
@@ -2742,17 +2740,17 @@
         <v>135</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="20"/>
       <c r="F22" s="20"/>
       <c r="G22" s="19"/>
       <c r="H22" s="33" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I22" s="20"/>
       <c r="J22" s="9" t="s">
@@ -9488,10 +9486,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C2" t="s">
         <v>133</v>
